--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487843_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487843_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9876</v>
+        <v>5.233</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5072</v>
+        <v>6.459</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5196</v>
+        <v>-1.226</v>
       </c>
       <c r="G2" t="n">
         <v>3.6724</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7639</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3726</v>
+        <v>0.3244</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6087</v>
+        <v>-0.3151</v>
       </c>
       <c r="V2" t="n">
         <v>0.9268999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1142</v>
+        <v>2.9478</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0837</v>
+        <v>2.5356</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0305</v>
+        <v>0.4122</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1072</v>
@@ -688,13 +688,13 @@
         <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5162</v>
+        <v>-0.6826</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9663</v>
+        <v>-0.5143</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.1683</v>
       </c>
       <c r="V3" t="n">
         <v>1.8645</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8912</v>
+        <v>1.9755</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7596</v>
+        <v>2.932</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8685</v>
+        <v>-0.9565</v>
       </c>
       <c r="G4" t="n">
         <v>-0.668</v>
@@ -766,13 +766,13 @@
         <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0059</v>
+        <v>0.0785</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3372</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5037</v>
+        <v>0.4156</v>
       </c>
       <c r="V4" t="n">
         <v>2.565</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MARTIN MARTIN</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2287</v>
+        <v>-0.0289</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3352</v>
+        <v>2.2409</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5639</v>
+        <v>-2.2697</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2222</v>
+        <v>1.7166</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4157</v>
+        <v>0.5458</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1935</v>
+        <v>1.1708</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7088</v>
+        <v>2.9659</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2664</v>
+        <v>1.7993</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5576</v>
+        <v>1.1667</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.931</v>
+        <v>-1.2494</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6821</v>
+        <v>-1.2535</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7511</v>
+        <v>0.0041</v>
       </c>
       <c r="P5" t="n">
         <v>0.2081</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2427</v>
+        <v>-0.4216</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3962</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8299</v>
+        <v>-0.0254</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.532</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5838</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5838</v>
+        <v>-2.4518</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>P. MARTIN MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2753</v>
+        <v>-0.0458</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7889</v>
+        <v>-0.2281</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0642</v>
+        <v>0.1822</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7166</v>
+        <v>-0.2222</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5458</v>
+        <v>-0.4157</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1708</v>
+        <v>0.1935</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9659</v>
+        <v>0.7088</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7993</v>
+        <v>1.2664</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1667</v>
+        <v>-0.5576</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2494</v>
+        <v>-0.931</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2535</v>
+        <v>-1.6821</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0041</v>
+        <v>0.7511</v>
       </c>
       <c r="P6" t="n">
         <v>0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.668</v>
+        <v>-0.0318</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8482</v>
+        <v>-0.48</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1801</v>
+        <v>0.4482</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.532</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.5838</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4518</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9201</v>
+        <v>-0.3928</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.87</v>
+        <v>-0.1642</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0502</v>
+        <v>-0.2287</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3879</v>
+        <v>1.8486</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5715</v>
+        <v>0.0721</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8164</v>
+        <v>1.7765</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4693</v>
+        <v>2.8368</v>
       </c>
       <c r="K7" t="n">
-        <v>0.245</v>
+        <v>1.7093</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7144</v>
+        <v>1.1275</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9186</v>
+        <v>-0.9881</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8165</v>
+        <v>-1.6372</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.102</v>
+        <v>0.6491</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8325</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2081</v>
+        <v>-3.3299</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8246</v>
+        <v>-1.4816</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6524</v>
+        <v>-0.4848</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1722</v>
+        <v>-0.9968</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4599</v>
+        <v>0.697</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4599</v>
+        <v>0.8137</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9807</v>
+        <v>-0.47</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5027</v>
+        <v>1.9547</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4834</v>
+        <v>-2.4247</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2229</v>
@@ -1078,13 +1078,13 @@
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0791</v>
+        <v>-0.5684</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7053</v>
+        <v>-0.2533</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3738</v>
+        <v>-0.3151</v>
       </c>
       <c r="V8" t="n">
         <v>0.1132</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0041</v>
+        <v>-0.9598</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.658</v>
+        <v>-0.7628</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3461</v>
+        <v>-0.197</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8486</v>
+        <v>-1.3879</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0721</v>
+        <v>-0.5715</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7765</v>
+        <v>-0.8164</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8368</v>
+        <v>-0.4693</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7093</v>
+        <v>0.245</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1275</v>
+        <v>-0.7144</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9881</v>
+        <v>-0.9186</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6372</v>
+        <v>-0.8165</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6491</v>
+        <v>-0.102</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.3299</v>
+        <v>-0.2081</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0929</v>
+        <v>-0.8643</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9786</v>
+        <v>-0.5453</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1143</v>
+        <v>-0.319</v>
       </c>
       <c r="V9" t="n">
-        <v>0.697</v>
+        <v>0.4599</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8137</v>
+        <v>0.4599</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1754</v>
+        <v>-1.4675</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1142</v>
+        <v>-0.2072</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2897</v>
+        <v>-1.2603</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6881</v>
@@ -1234,13 +1234,13 @@
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8005</v>
+        <v>-1.0926</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2577</v>
+        <v>-0.0638</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0582</v>
+        <v>-1.0288</v>
       </c>
       <c r="V10" t="n">
         <v>2.1051</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7215</v>
+        <v>-2.1208</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0675</v>
+        <v>-1.4961</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6541</v>
+        <v>-0.6247</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4149</v>
@@ -1312,13 +1312,13 @@
         <v>0.2081</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5258</v>
+        <v>0.1266</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6491</v>
+        <v>0.2205</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1233</v>
+        <v>-0.0939</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0523</v>
+        <v>-3.9261</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7539</v>
+        <v>-2.5396</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2984</v>
+        <v>-1.3865</v>
       </c>
       <c r="G12" t="n">
         <v>-3.1797</v>
@@ -1390,13 +1390,13 @@
         <v>1.2487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8507</v>
+        <v>-0.7245</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5748</v>
+        <v>-0.3605</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2759</v>
+        <v>-0.364</v>
       </c>
       <c r="V12" t="n">
         <v>-0.23</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.09229999999999894</v>
+        <v>0.7446000000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0717</v>
+        <v>10.7242</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.979800000000001</v>
+        <v>-9.979699999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.6533</v>
+        <v>-2.653300000000001</v>
       </c>
       <c r="H13" t="n">
         <v>-4.2863</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6329</v>
+        <v>1.632900000000001</v>
       </c>
       <c r="J13" t="n">
         <v>13.0854</v>
@@ -1447,7 +1447,7 @@
         <v>8.4725</v>
       </c>
       <c r="L13" t="n">
-        <v>4.612699999999999</v>
+        <v>4.612699999999998</v>
       </c>
       <c r="M13" t="n">
         <v>-15.7387</v>
@@ -1468,10 +1468,10 @@
         <v>13.5276</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.3055</v>
+        <v>-5.653</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.543</v>
+        <v>-2.8905</v>
       </c>
       <c r="U13" t="n">
         <v>-2.7626</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2073</v>
+        <v>6.1676</v>
       </c>
       <c r="E14" t="n">
-        <v>5.045</v>
+        <v>5.1522</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1622</v>
+        <v>1.0154</v>
       </c>
       <c r="G14" t="n">
         <v>4.4628</v>
@@ -1546,13 +1546,13 @@
         <v>0.6244</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2161</v>
+        <v>1.1764</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8416</v>
+        <v>0.9487</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3745</v>
+        <v>0.2277</v>
       </c>
       <c r="V14" t="n">
         <v>0.9446</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7429</v>
+        <v>2.1907</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9034</v>
+        <v>1.1701</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1604</v>
+        <v>1.0207</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6284</v>
+        <v>-2.2621</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.8592</v>
+        <v>-0.7035</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4876</v>
+        <v>-1.5586</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0369</v>
+        <v>-2.4783</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6996</v>
+        <v>-0.3114</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7365</v>
+        <v>-2.1668</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4085</v>
+        <v>0.2162</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1596</v>
+        <v>-0.3921</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7511</v>
+        <v>0.6082</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3186</v>
+        <v>0.3696</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0746</v>
+        <v>0.1458</v>
       </c>
       <c r="U15" t="n">
-        <v>0.244</v>
+        <v>0.2238</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0366</v>
+        <v>3.0427</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.5026</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0366</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4812</v>
+        <v>2.1754</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9558</v>
+        <v>2.0461</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5255</v>
+        <v>0.1292</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2621</v>
+        <v>0.6284</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7035</v>
+        <v>-1.8592</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5586</v>
+        <v>2.4876</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.4783</v>
+        <v>1.0369</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3114</v>
+        <v>-0.6996</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.1668</v>
+        <v>1.7365</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2162</v>
+        <v>-0.4085</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3921</v>
+        <v>-1.1596</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6082</v>
+        <v>0.7511</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R16" t="n">
         <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3399</v>
+        <v>1.751</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.06850000000000001</v>
+        <v>1.2173</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2714</v>
+        <v>0.5337</v>
       </c>
       <c r="V16" t="n">
-        <v>3.0427</v>
+        <v>-1.0366</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5026</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4599</v>
+        <v>-1.0366</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1233</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.2474</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8742</v>
+        <v>0.3164</v>
       </c>
       <c r="G17" t="n">
         <v>3.9487</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2716</v>
+        <v>1.4638</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1338</v>
+        <v>0.6163</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4054</v>
+        <v>0.8475</v>
       </c>
       <c r="V17" t="n">
         <v>-2.2218</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.358</v>
+        <v>-0.1643</v>
       </c>
       <c r="E18" t="n">
-        <v>4.2116</v>
+        <v>0.5951</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.5696</v>
+        <v>-0.7594</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1121</v>
+        <v>1.0393</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6543</v>
+        <v>0.578</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5422</v>
+        <v>0.4613</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1902</v>
+        <v>2.8192</v>
       </c>
       <c r="K18" t="n">
-        <v>2.524</v>
+        <v>1.1129</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6662</v>
+        <v>1.7063</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0781</v>
+        <v>-1.78</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8697</v>
+        <v>-0.5349</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2084</v>
+        <v>-1.245</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0406</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2081</v>
+        <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0543</v>
+        <v>0.0264</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0619</v>
+        <v>-0.3729</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.3993</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.565</v>
+        <v>-0.8137</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.7325</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3766</v>
+        <v>-0.4998</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7367</v>
+        <v>-0.7811</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1133</v>
+        <v>0.2813</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.191</v>
+        <v>-1.0977</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0318</v>
+        <v>-0.1343</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1592</v>
+        <v>-0.9634</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5443</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1727</v>
+        <v>0.0576</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3716</v>
+        <v>-0.7144</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7352</v>
+        <v>-0.4409</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2044</v>
+        <v>-0.1919</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5308</v>
+        <v>-0.249</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q19" t="n">
+        <v>-0.2081</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.0838</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="V19" t="n">
         <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.8325</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.5656</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.1924</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.3732</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.5838</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6976</v>
+        <v>-0.6433</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3808</v>
+        <v>1.4152</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0784</v>
+        <v>-2.0585</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0393</v>
+        <v>-1.191</v>
       </c>
       <c r="H20" t="n">
-        <v>0.578</v>
+        <v>-1.0318</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4613</v>
+        <v>-0.1592</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8192</v>
+        <v>1.5443</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1129</v>
+        <v>0.1727</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7063</v>
+        <v>1.3716</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.78</v>
+        <v>-2.7352</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5349</v>
+        <v>-1.2044</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.245</v>
+        <v>-1.5308</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5069</v>
+        <v>0.299</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.129</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0803</v>
+        <v>0.428</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8137</v>
+        <v>-0.5838</v>
       </c>
       <c r="W20" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0437</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7728</v>
+        <v>-1.139</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9954</v>
+        <v>3.7829</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2226</v>
+        <v>-4.9219</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0977</v>
+        <v>0.1121</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1343</v>
+        <v>1.6543</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9634</v>
+        <v>-1.5422</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6568000000000001</v>
+        <v>3.1902</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0576</v>
+        <v>2.524</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7144</v>
+        <v>0.6662</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4409</v>
+        <v>-3.0781</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1919</v>
+        <v>-0.8697</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.249</v>
+        <v>-2.2084</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.2081</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.2734</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1305</v>
+        <v>-0.3667</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0391</v>
+        <v>0.64</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.565</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-3.7325</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1092</v>
+        <v>-1.6997</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5889</v>
+        <v>-0.2674</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5203</v>
+        <v>-1.4322</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5979</v>
@@ -2170,13 +2170,13 @@
         <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.227</v>
+        <v>0.1825</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3915</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1644</v>
+        <v>0.2525</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1168</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8711</v>
+        <v>-2.8434</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1588</v>
+        <v>-2.4057</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7123</v>
+        <v>-0.4377</v>
       </c>
       <c r="G23" t="n">
-        <v>1.157</v>
+        <v>-1.5464</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9915</v>
+        <v>-0.5373</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8345</v>
+        <v>-1.0091</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5658</v>
+        <v>-1.73</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2982</v>
+        <v>-0.2922</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7323</v>
+        <v>-1.4377</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4088</v>
+        <v>0.1836</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3066</v>
+        <v>-0.245</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1022</v>
+        <v>0.4286</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9137</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.3705</v>
+        <v>-1.0406</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.6623</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6458</v>
+        <v>0.3648</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1077</v>
+        <v>0.2975</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.868</v>
+        <v>-1.7513</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.868</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2148</v>
+        <v>-2.991</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5129</v>
+        <v>-0.4803</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.702</v>
+        <v>-2.5107</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5464</v>
+        <v>1.157</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5373</v>
+        <v>2.9915</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0091</v>
+        <v>-1.8345</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.73</v>
+        <v>3.5658</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2922</v>
+        <v>4.2982</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4377</v>
+        <v>-0.7323</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1836</v>
+        <v>-2.4088</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.245</v>
+        <v>-1.3066</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4286</v>
+        <v>-1.1022</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2081</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0406</v>
+        <v>-4.3705</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S24" t="n">
-        <v>0.291</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2577</v>
+        <v>0.3244</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0333</v>
+        <v>0.3093</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.7513</v>
+        <v>-1.868</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.7513</v>
+        <v>-1.868</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.09199999999999831</v>
+        <v>0.6221999999999981</v>
       </c>
       <c r="E25" t="n">
-        <v>9.979799999999997</v>
+        <v>9.979699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.0718</v>
+        <v>-9.357399999999998</v>
       </c>
       <c r="G25" t="n">
         <v>2.653199999999999</v>
@@ -2389,10 +2389,10 @@
         <v>-13.0854</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.472499999999998</v>
+        <v>-8.4725</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.6129</v>
+        <v>-4.612900000000001</v>
       </c>
       <c r="P25" t="n">
         <v>-2.0811</v>
@@ -2404,13 +2404,13 @@
         <v>11.4466</v>
       </c>
       <c r="S25" t="n">
-        <v>6.3056</v>
+        <v>7.0197</v>
       </c>
       <c r="T25" t="n">
         <v>2.7625</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5429</v>
+        <v>4.2572</v>
       </c>
       <c r="V25" t="n">
         <v>-6.9697</v>
